--- a/E-Commerce Store ( Dash-Board ) Final Project.xlsx
+++ b/E-Commerce Store ( Dash-Board ) Final Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zaki DA\Excel-Data-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C66BDDF-3777-4CA9-8478-DDF06C52B176}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8796E75D-8BBE-411A-B4E9-1F270E6A449C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7005" activeTab="3" xr2:uid="{14B0D23D-F240-47E8-8177-FC14410B2B8F}"/>
   </bookViews>
@@ -1144,84 +1144,3594 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="1203">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="[$₹-4009]\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="[$₹-4009]\ 0.00,\ &quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="[$₹-4009]\ 0.00,,\ &quot;M&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
@@ -1285,8 +4795,8 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="new" pivot="0" table="0" count="10" xr9:uid="{1D55CC3D-6632-49BE-A653-694B848941F1}">
-      <tableStyleElement type="wholeTable" dxfId="32"/>
-      <tableStyleElement type="headerRow" dxfId="31"/>
+      <tableStyleElement type="wholeTable" dxfId="1202"/>
+      <tableStyleElement type="headerRow" dxfId="1201"/>
     </tableStyle>
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="5" xr9:uid="{063CC953-61A3-4EF5-A467-EB56AD4882B8}"/>
   </tableStyles>
@@ -9104,8 +12614,8 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
           <xdr:graphicFrame macro="">
             <xdr:nvGraphicFramePr>
               <xdr:cNvPr id="29" name="gender">
@@ -9128,7 +12638,7 @@
             </a:graphic>
           </xdr:graphicFrame>
         </mc:Choice>
-        <mc:Fallback>
+        <mc:Fallback xmlns="">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
               <xdr:cNvPr id="0" name=""/>
@@ -9167,8 +12677,8 @@
           </xdr:sp>
         </mc:Fallback>
       </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
           <xdr:graphicFrame macro="">
             <xdr:nvGraphicFramePr>
               <xdr:cNvPr id="38" name="Years">
@@ -9191,7 +12701,7 @@
             </a:graphic>
           </xdr:graphicFrame>
         </mc:Choice>
-        <mc:Fallback>
+        <mc:Fallback xmlns="">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
               <xdr:cNvPr id="0" name=""/>
@@ -9323,8 +12833,8 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
           <xdr:graphicFrame macro="">
             <xdr:nvGraphicFramePr>
               <xdr:cNvPr id="19" name="category">
@@ -9347,7 +12857,7 @@
             </a:graphic>
           </xdr:graphicFrame>
         </mc:Choice>
-        <mc:Fallback>
+        <mc:Fallback xmlns="">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
               <xdr:cNvPr id="0" name=""/>
@@ -9386,8 +12896,8 @@
           </xdr:sp>
         </mc:Fallback>
       </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
           <xdr:graphicFrame macro="">
             <xdr:nvGraphicFramePr>
               <xdr:cNvPr id="24" name="payment_method">
@@ -9410,7 +12920,7 @@
             </a:graphic>
           </xdr:graphicFrame>
         </mc:Choice>
-        <mc:Fallback>
+        <mc:Fallback xmlns="">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
               <xdr:cNvPr id="0" name=""/>
@@ -13045,870 +16555,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFFA87BA-457C-403D-8449-7806FD605099}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
-  <location ref="N3:O16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="24">
-        <item m="1" x="19"/>
-        <item m="1" x="14"/>
-        <item m="1" x="13"/>
-        <item m="1" x="21"/>
-        <item x="4"/>
-        <item m="1" x="12"/>
-        <item m="1" x="22"/>
-        <item m="1" x="15"/>
-        <item m="1" x="17"/>
-        <item m="1" x="16"/>
-        <item m="1" x="18"/>
-        <item m="1" x="20"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="2">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="8" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="0">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="31" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="32" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{289060AB-A324-4319-A532-791A245E5299}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
-  <location ref="K3:L8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0" numFmtId="168"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="25">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="23">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="6">
-    <chartFormat chart="14" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="20" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED6098FC-1E25-4624-A558-D4041208EDE0}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="51">
-  <location ref="T3:U9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of customer_age" fld="13" subtotal="count" baseField="9" baseItem="1"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="5">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="47" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="48" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="49" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="50" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85926FF3-8FA2-4B6E-A290-01922D80BBA4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="93">
-  <location ref="T13:U19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
-      <items count="26">
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="22"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="18"/>
-        <item x="24"/>
-        <item x="15"/>
-        <item x="13"/>
-        <item x="5"/>
-        <item x="19"/>
-        <item x="0"/>
-        <item x="12"/>
-        <item x="7"/>
-        <item x="21"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="9">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="5">
-            <x v="3"/>
-            <x v="6"/>
-            <x v="14"/>
-            <x v="19"/>
-            <x v="22"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="6">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="5">
-    <chartFormat chart="81" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="82" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="89" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="90" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="92" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="9" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="5" filterVal="5"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{231DF382-F8CB-486A-9E93-5E983162472A}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="63">
   <location ref="W3:X9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
@@ -14029,13 +16675,13 @@
     <dataField name="Count of  Amount" fld="5" subtotal="count" baseField="11" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="12">
+    <format dxfId="1172">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="1171">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="1170">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -14269,7 +16915,391 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F0EC064-73CA-493C-8DEB-E83E69BE6B1A}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="41">
+  <location ref="K12:L17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="24">
+        <item m="1" x="19"/>
+        <item m="1" x="14"/>
+        <item m="1" x="13"/>
+        <item m="1" x="21"/>
+        <item x="4"/>
+        <item m="1" x="12"/>
+        <item m="1" x="22"/>
+        <item m="1" x="15"/>
+        <item m="1" x="17"/>
+        <item m="1" x="16"/>
+        <item m="1" x="18"/>
+        <item m="1" x="20"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of  Amount" fld="5" subtotal="count" baseField="13" baseItem="1"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1195">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1194">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="34" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="37" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{289060AB-A324-4319-A532-791A245E5299}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+  <location ref="K3:L8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0" numFmtId="168"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="1175">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1174">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1173">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="6">
+    <chartFormat chart="14" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="20" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4FAE3F3A-585A-4543-981F-80C1442F0180}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="63">
   <location ref="Z3:AA8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
@@ -14387,16 +17417,16 @@
     <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="16">
+    <format dxfId="1179">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="1178">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="1177">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="1176">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14412,7 +17442,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F76B69F-68B3-435E-A8A7-D96FC9E0E45B}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="65">
   <location ref="Q3:R29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
@@ -14631,10 +17661,10 @@
     <dataField name="Count of customer_age" fld="13" subtotal="count" baseField="9" baseItem="1"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="20">
+    <format dxfId="1183">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="1182">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="1">
@@ -14643,15 +17673,429 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="1181">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="1180">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="1">
     <chartFormat chart="60" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFFA87BA-457C-403D-8449-7806FD605099}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34">
+  <location ref="N3:O16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="24">
+        <item m="1" x="19"/>
+        <item m="1" x="14"/>
+        <item m="1" x="13"/>
+        <item m="1" x="21"/>
+        <item x="4"/>
+        <item m="1" x="12"/>
+        <item m="1" x="22"/>
+        <item m="1" x="15"/>
+        <item m="1" x="17"/>
+        <item m="1" x="16"/>
+        <item m="1" x="18"/>
+        <item m="1" x="20"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="1186">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1185">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1184">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="31" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED6098FC-1E25-4624-A558-D4041208EDE0}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="51">
+  <location ref="T3:U9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of customer_age" fld="13" subtotal="count" baseField="9" baseItem="1"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="1189">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1188">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1187">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="47" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="48" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="49" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="50" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14803,6 +18247,256 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85926FF3-8FA2-4B6E-A290-01922D80BBA4}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="93">
+  <location ref="T13:U19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
+      <items count="26">
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="22"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="19"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="7"/>
+        <item x="21"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of  Amount" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="1193">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1192">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="1191">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="5">
+            <x v="3"/>
+            <x v="6"/>
+            <x v="14"/>
+            <x v="19"/>
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1190">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="5">
+    <chartFormat chart="81" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="82" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="89" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="90" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="92" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="9" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4EDCADA-02F1-492D-8FAB-7386D73B236C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H3:I6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
@@ -14913,190 +18607,6 @@
   <dataFields count="1">
     <dataField name="Count of product_name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F0EC064-73CA-493C-8DEB-E83E69BE6B1A}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="41">
-  <location ref="K12:L17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="24">
-        <item m="1" x="19"/>
-        <item m="1" x="14"/>
-        <item m="1" x="13"/>
-        <item m="1" x="21"/>
-        <item x="4"/>
-        <item m="1" x="12"/>
-        <item m="1" x="22"/>
-        <item m="1" x="15"/>
-        <item m="1" x="17"/>
-        <item m="1" x="16"/>
-        <item m="1" x="18"/>
-        <item m="1" x="20"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of  Amount" fld="5" subtotal="count" baseField="13" baseItem="1"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="22">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="34" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="37" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -15261,14 +18771,14 @@
     <tableColumn id="1" xr3:uid="{4158B185-1485-4493-B39B-02E1D78F78E2}" uniqueName="1" name="order_id" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{94DF2468-6389-4C9D-8E71-9C9EAF65A54A}" uniqueName="2" name="product_name" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2FC4F5A9-A3A7-4D3E-B142-6AD018665AA3}" uniqueName="3" name="category" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{FE32D6FF-91EA-4EC3-B782-CF8933449679}" uniqueName="4" name="price" queryTableFieldId="4" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{FE32D6FF-91EA-4EC3-B782-CF8933449679}" uniqueName="4" name="price" queryTableFieldId="4" dataDxfId="1200"/>
     <tableColumn id="5" xr3:uid="{5940DE25-3C99-4DB0-BA1C-CABA75E1E550}" uniqueName="5" name="qty" queryTableFieldId="5"/>
-    <tableColumn id="13" xr3:uid="{16B9E454-2EEC-4A10-860F-0B7862FB0FBE}" uniqueName="13" name=" Amount" queryTableFieldId="13" dataDxfId="29">
+    <tableColumn id="13" xr3:uid="{16B9E454-2EEC-4A10-860F-0B7862FB0FBE}" uniqueName="13" name=" Amount" queryTableFieldId="13" dataDxfId="1199">
       <calculatedColumnFormula>ecommerce_store_dataset[[#This Row],[price]]*ecommerce_store_dataset[[#This Row],[qty]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E27E0975-1438-4EA9-800E-F032F0A0A535}" uniqueName="6" name="order_date" queryTableFieldId="6" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{F6905510-B432-44DB-9AA2-120B2992FA94}" uniqueName="7" name="Delivery_date" queryTableFieldId="7" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{834936BB-FDA5-42E3-B211-1E8ADDB5FBA3}" uniqueName="14" name="Month" queryTableFieldId="14" dataDxfId="26">
+    <tableColumn id="6" xr3:uid="{E27E0975-1438-4EA9-800E-F032F0A0A535}" uniqueName="6" name="order_date" queryTableFieldId="6" dataDxfId="1198"/>
+    <tableColumn id="7" xr3:uid="{F6905510-B432-44DB-9AA2-120B2992FA94}" uniqueName="7" name="Delivery_date" queryTableFieldId="7" dataDxfId="1197"/>
+    <tableColumn id="14" xr3:uid="{834936BB-FDA5-42E3-B211-1E8ADDB5FBA3}" uniqueName="14" name="Month" queryTableFieldId="14" dataDxfId="1196">
       <calculatedColumnFormula>TEXT(ecommerce_store_dataset[[#This Row],[Delivery_date]],"mmm")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{C648F6F6-9DFC-41F3-8313-6AFF1EA0F17B}" uniqueName="8" name="city" queryTableFieldId="8"/>
